--- a/artfynd/A 11909-2024 artfynd.xlsx
+++ b/artfynd/A 11909-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -808,14 +808,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66549907</v>
+        <v>89378409</v>
       </c>
       <c r="B3" t="n">
         <v>104838</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -843,25 +843,22 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vägkant väst Asktjärnet, Vrm</t>
+          <t>Lacketorpet, S631, norr om väg, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>336938.9803120741</v>
+        <v>336935.1678344107</v>
       </c>
       <c r="R3" t="n">
-        <v>6633505.14910789</v>
+        <v>6633498.767506616</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +882,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
+          <t>2020-06-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -895,12 +892,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
+          <t>2020-06-09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ca 60 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,148 +911,27 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jeanette Fahlstad</t>
+          <t>Isabelle Dekhla</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jeanette Fahlstad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>89378409</v>
-      </c>
-      <c r="B4" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>219955</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Slåttergubbe</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Arnica montana</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Lacketorpet, S631, norr om väg, Vrm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>336935.1678344107</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6633498.767506616</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Eda</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Järnskog</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2020-06-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2020-06-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ca 60 bladrosetter</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Isabelle Dekhla</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
           <t>Rasmus Andgren Ullberg, Johanna Ek</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 11909-2024 artfynd.xlsx
+++ b/artfynd/A 11909-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -937,6 +937,138 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126365957</v>
+      </c>
+      <c r="B4" t="n">
+        <v>107026</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lacketorpet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>336929</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6633495</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>4 blommade exemplar och ett 50 tal bladrosetter på den norra sidan av vägen i dikesbotten och ytterslänt.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Malin Schött</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Malin Schött</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11909-2024 artfynd.xlsx
+++ b/artfynd/A 11909-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1069,6 +1069,134 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126378512</v>
+      </c>
+      <c r="B5" t="n">
+        <v>107026</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lacketorpet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>336943</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6633500</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>4 blommande ex men ca 50 bladrosetter. I dikesbotten och ytterslänt på norra sidan av vägen.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna Ljunggren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna Ljunggren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11909-2024 artfynd.xlsx
+++ b/artfynd/A 11909-2024 artfynd.xlsx
@@ -942,7 +942,7 @@
         <v>126365957</v>
       </c>
       <c r="B4" t="n">
-        <v>107026</v>
+        <v>107035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>126378512</v>
       </c>
       <c r="B5" t="n">
-        <v>107026</v>
+        <v>107035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
